--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104693_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104693_W27.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.329499999999999</v>
+        <v>6.9615</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2883</v>
+        <v>4.4465</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0412</v>
+        <v>2.515</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5522</v>
+        <v>5.5481</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9582</v>
+        <v>3.9496</v>
       </c>
       <c r="I2" t="n">
-        <v>1.594</v>
+        <v>1.5986</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1911</v>
+        <v>5.1578</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1489</v>
+        <v>4.1229</v>
       </c>
       <c r="L2" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3611</v>
+        <v>0.3903</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.802</v>
+        <v>0.4345</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3902</v>
+        <v>-0.4138</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4118</v>
+        <v>0.8484</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5426</v>
+        <v>4.8529</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8389</v>
+        <v>1.6991</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7037</v>
+        <v>3.1538</v>
       </c>
       <c r="G3" t="n">
-        <v>3.043</v>
+        <v>3.0402</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2135</v>
+        <v>3.2084</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1706</v>
+        <v>-0.1682</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3064</v>
+        <v>1.2734</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6179</v>
+        <v>2.592</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3115</v>
+        <v>-1.3186</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7365</v>
+        <v>1.7668</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1562</v>
+        <v>-0.849</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8135</v>
+        <v>-0.911</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3427</v>
+        <v>0.062</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6396</v>
+        <v>3.5772</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6971</v>
+        <v>-1.2952</v>
       </c>
       <c r="F4" t="n">
-        <v>5.3367</v>
+        <v>4.8725</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0526</v>
+        <v>2.067</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4501</v>
+        <v>1.4558</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6025</v>
+        <v>0.6111</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1766</v>
+        <v>-0.1893</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4604</v>
+        <v>0.4514</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2292</v>
+        <v>2.2562</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9896</v>
+        <v>1.0044</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2014</v>
+        <v>0.1233</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2521</v>
+        <v>-0.8296</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4535</v>
+        <v>0.9529</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5031</v>
+        <v>2.9119</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4111</v>
+        <v>1.6853</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0919</v>
+        <v>1.2266</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2648</v>
+        <v>3.2617</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6522</v>
+        <v>1.6515</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6126</v>
+        <v>1.6102</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1865</v>
+        <v>3.1583</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0248</v>
+        <v>1.0062</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1617</v>
+        <v>2.1521</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0784</v>
+        <v>0.1033</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3911</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3217</v>
+        <v>-1.0178</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9306</v>
+        <v>1.0259</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1322</v>
+        <v>2.5728</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.329</v>
+        <v>-1.9625</v>
       </c>
       <c r="F6" t="n">
-        <v>4.4611</v>
+        <v>4.5353</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2172</v>
+        <v>2.2022</v>
       </c>
       <c r="H6" t="n">
-        <v>1.215</v>
+        <v>1.2122</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0021</v>
+        <v>0.9901</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9283</v>
+        <v>0.8788</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7926</v>
+        <v>0.7682</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1357</v>
+        <v>0.1106</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2888</v>
+        <v>1.3234</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4224</v>
+        <v>0.444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2192</v>
+        <v>-0.7675999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6695</v>
+        <v>-1.2478</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4503</v>
+        <v>0.4802</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.444</v>
+        <v>1.1498</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7091</v>
+        <v>-1.2299</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1531</v>
+        <v>2.3797</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7228</v>
+        <v>0.7085</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6606</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3834</v>
+        <v>1.3854</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0581</v>
+        <v>0.0155</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6184</v>
+        <v>-1.6525</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6647</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9578</v>
+        <v>0.9755</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6248</v>
+        <v>0.1046</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3912</v>
+        <v>-0.8506</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7664</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1145</v>
+        <v>-0.978</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.3788</v>
+        <v>-3.1451</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2644</v>
+        <v>2.1671</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3194</v>
+        <v>-0.3185</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0577</v>
+        <v>-1.0542</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7383</v>
+        <v>0.7358</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3918</v>
+        <v>-1.4099</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.0878</v>
+        <v>-1.0967</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0724</v>
+        <v>1.0914</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1561</v>
+        <v>-0.0253</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>-0.3695</v>
       </c>
       <c r="U8" t="n">
-        <v>0.47</v>
+        <v>0.3441</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DRELL</t>
+          <t>G. VIVES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6527</v>
+        <v>-1.5701</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.933</v>
+        <v>-1.6626</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2803</v>
+        <v>0.0925</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0063</v>
+        <v>-1.4666</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0228</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0985</v>
+        <v>-1.4895</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7379</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0.0517</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>-0.7896</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5869</v>
+        <v>-0.7287</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7228</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1359</v>
+        <v>-0.6998</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3536</v>
+        <v>-0.3311</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0212</v>
+        <v>-0.697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3324</v>
+        <v>0.3659</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. VIVES</t>
+          <t>H. DRELL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7952</v>
+        <v>-1.645</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6569</v>
+        <v>-2.2955</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1384</v>
+        <v>0.6505</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4725</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0202</v>
+        <v>0.0974</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4927</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.052</v>
+        <v>-0.6345</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7381</v>
+        <v>0.6073</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0318</v>
+        <v>0.7319</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7063</v>
+        <v>-0.1246</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5495</v>
+        <v>0.345</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.3324</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1461</v>
+        <v>0.6774</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9739</v>
+        <v>-2.0684</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4278</v>
+        <v>-3.4473</v>
       </c>
       <c r="F11" t="n">
-        <v>1.454</v>
+        <v>1.3789</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0504</v>
+        <v>-1.051</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-0.6028</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4531</v>
+        <v>-0.4482</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6696</v>
+        <v>-0.6802</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7069</v>
+        <v>-0.7174</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3808</v>
+        <v>-0.3708</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0765</v>
+        <v>-0.0174</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.6273</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7026</v>
+        <v>0.6099</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.0547</v>
+        <v>15.7646</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.593400000000001</v>
+        <v>-7.207199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>22.648</v>
+        <v>22.97190000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>14.004</v>
+        <v>14.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>9.2859</v>
+        <v>9.2638</v>
       </c>
       <c r="I12" t="n">
-        <v>4.718</v>
+        <v>4.737900000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>7.104800000000001</v>
+        <v>6.869200000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>5.052999999999998</v>
+        <v>4.891299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>2.051800000000001</v>
+        <v>1.978</v>
       </c>
       <c r="M12" t="n">
-        <v>6.899100000000001</v>
+        <v>7.1322</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2327</v>
+        <v>4.3722</v>
       </c>
       <c r="O12" t="n">
-        <v>2.666399999999999</v>
+        <v>2.76</v>
       </c>
       <c r="P12" t="n">
-        <v>5.670999999999999</v>
+        <v>5.690899999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0126</v>
+        <v>17.0726</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6634</v>
+        <v>-0.9747999999999998</v>
       </c>
       <c r="T12" t="n">
-        <v>-7.9844</v>
+        <v>-7.296799999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>6.321</v>
+        <v>6.3218</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.9565</v>
+        <v>-2.9529</v>
       </c>
       <c r="W12" t="n">
-        <v>4.628</v>
+        <v>4.602099999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.5845</v>
+        <v>-7.5549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8379</v>
+        <v>1.736</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0968</v>
+        <v>-0.8071</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2589</v>
+        <v>2.5431</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.826</v>
+        <v>0.2179</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.117</v>
+        <v>0.1318</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.709</v>
+        <v>0.0861</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9134</v>
+        <v>-1.0879</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6624</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.749</v>
+        <v>-1.1773</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7393</v>
+        <v>1.3058</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7794</v>
+        <v>0.0424</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04</v>
+        <v>1.2634</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6639</v>
+        <v>-0.0267</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0907</v>
+        <v>-0.8087</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.782</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7232</v>
+        <v>1.4531</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.0189</v>
+        <v>1.8475</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7421</v>
+        <v>-0.3945</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2201</v>
+        <v>-0.8198</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1269</v>
+        <v>-0.1123</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09320000000000001</v>
+        <v>-0.7075</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0681</v>
+        <v>0.9023</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0968</v>
+        <v>1.6547</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1649</v>
+        <v>-0.7524</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2883</v>
+        <v>-1.7221</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0301</v>
+        <v>-1.767</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2582</v>
+        <v>0.0449</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0433</v>
+        <v>0.2728</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0434</v>
+        <v>-0.1443</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0002</v>
+        <v>0.4171</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. EDWARDS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2246</v>
+        <v>1.111</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4714</v>
+        <v>-2.1251</v>
       </c>
       <c r="F15" t="n">
-        <v>1.696</v>
+        <v>3.2362</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4856</v>
+        <v>0.405</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9712</v>
+        <v>-0.9625</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5144</v>
+        <v>1.3675</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.227</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-1.4931</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>1.2661</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8258</v>
+        <v>0.632</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2368</v>
+        <v>0.5306</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5891</v>
+        <v>0.1014</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6194</v>
+        <v>0.2508</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2299</v>
+        <v>-0.7599</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3895</v>
+        <v>1.0107</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8639</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>J. EDWARDS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5606</v>
+        <v>0.9404</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.4645</v>
+        <v>-0.8355</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0251</v>
+        <v>1.7759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3991</v>
+        <v>-1.4804</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9683</v>
+        <v>-0.9681</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3674</v>
+        <v>-0.5123</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2174</v>
+        <v>-0.6635</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4861</v>
+        <v>-0.7379</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2688</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6165</v>
+        <v>-0.8169</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5178</v>
+        <v>-0.2301</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.5868</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2922</v>
+        <v>0.3297</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.113</v>
+        <v>-0.1233</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8208</v>
+        <v>0.4531</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8634</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4323</v>
+        <v>-0.0169</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7374</v>
+        <v>-2.3923</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3051</v>
+        <v>2.3754</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1034</v>
+        <v>0.1353</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4877</v>
+        <v>-1.3529</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6157</v>
+        <v>1.4882</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3472</v>
+        <v>-0.7403999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>1.198</v>
+        <v>-1.1796</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>0.4392</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4506</v>
+        <v>0.8757</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6857</v>
+        <v>-0.1733</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7649</v>
+        <v>1.049</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.5138</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.8168</v>
+      </c>
+      <c r="V17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.9073</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.1747</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.3902</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.7845</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.5463</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.2677</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.7103</v>
+        <v>1.1297</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6321</v>
+        <v>-1.3974</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4648</v>
+        <v>-1.0956</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.59</v>
+        <v>-0.4882</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1253</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3272</v>
+        <v>1.3276</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2174</v>
+        <v>1.1786</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8902</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1375</v>
+        <v>-2.4232</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6274</v>
+        <v>-1.6668</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8571</v>
+        <v>0.4621</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3266</v>
+        <v>-0.1979</v>
       </c>
       <c r="U18" t="n">
-        <v>1.1837</v>
+        <v>0.66</v>
       </c>
       <c r="V18" t="n">
-        <v>2.571</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1207</v>
+        <v>-0.4601</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2495</v>
+        <v>-3.0037</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1287</v>
+        <v>2.5436</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1324</v>
+        <v>-1.4745</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.355</v>
+        <v>-1.5965</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4874</v>
+        <v>0.122</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7191</v>
+        <v>-1.3634</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1642</v>
+        <v>-2.2418</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4451</v>
+        <v>0.8783</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8515</v>
+        <v>-0.1111</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1908</v>
+        <v>0.6452</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0423</v>
+        <v>-0.7563</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2005</v>
+        <v>0.4972</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3962</v>
+        <v>-0.5625</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5967</v>
+        <v>1.0597</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2.5659</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6477</v>
+        <v>-2.8195</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0266</v>
+        <v>-1.4893</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6211</v>
+        <v>-1.3302</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6239</v>
+        <v>-0.629</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4213</v>
+        <v>-0.4249</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2026</v>
+        <v>-0.2041</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9576</v>
+        <v>0.9175</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9657</v>
+        <v>0.9405</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0081</v>
+        <v>-0.023</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5815</v>
+        <v>-1.5466</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.387</v>
+        <v>-1.3654</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.436</v>
+        <v>-0.5971</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.8086</v>
+        <v>-1.22</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3726</v>
+        <v>0.6229</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8282</v>
+        <v>-3.813</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.2496</v>
+        <v>-6.3958</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4214</v>
+        <v>2.5828</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6833</v>
+        <v>-2.6746</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0204</v>
+        <v>-0.0065</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6629</v>
+        <v>-2.6681</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.6067</v>
+        <v>-3.6241</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.9588</v>
+        <v>-2.9724</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9233</v>
+        <v>0.9495</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4676</v>
+        <v>0.4762</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5353</v>
+        <v>-0.6532</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0029</v>
+        <v>1.1294</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3839</v>
+        <v>-4.1057</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1432</v>
+        <v>-2.0411</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2407</v>
+        <v>-2.0646</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7064</v>
+        <v>-2.7017</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9365</v>
+        <v>-0.9336</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7699</v>
+        <v>-1.7681</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9293</v>
+        <v>-0.9388</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7771</v>
+        <v>-1.7629</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6094000000000001</v>
+        <v>-0.3357</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0166</v>
+        <v>0.1732</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.7746</v>
+        <v>-8.824999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1482</v>
+        <v>-6.859</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6264</v>
+        <v>-1.966</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8622</v>
+        <v>-3.8841</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.5453</v>
+        <v>-2.5501</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3169</v>
+        <v>-1.334</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5897</v>
+        <v>-1.6345</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.7255</v>
+        <v>-1.7451</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1357</v>
+        <v>0.1106</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2725</v>
+        <v>-2.2496</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0611</v>
+        <v>0.0395</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1825</v>
+        <v>-0.8296</v>
       </c>
       <c r="U23" t="n">
-        <v>1.2436</v>
+        <v>0.8691</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.0547</v>
+        <v>-15.0674</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.648</v>
+        <v>-22.9717</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5932</v>
+        <v>7.9043</v>
       </c>
       <c r="G24" t="n">
-        <v>-14.004</v>
+        <v>-14.0015</v>
       </c>
       <c r="H24" t="n">
-        <v>-9.2858</v>
+        <v>-9.2638</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.7181</v>
+        <v>-4.7377</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.8991</v>
+        <v>-7.132199999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.2328</v>
+        <v>-4.3724</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.666100000000001</v>
+        <v>-2.7599</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.1047</v>
+        <v>-6.8694</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.0531</v>
+        <v>-4.8914</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.0519</v>
+        <v>-1.9778</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0126</v>
+        <v>-17.0725</v>
       </c>
       <c r="R24" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6634</v>
+        <v>1.6719</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.320900000000001</v>
+        <v>-6.3221</v>
       </c>
       <c r="U24" t="n">
-        <v>7.9842</v>
+        <v>7.994</v>
       </c>
       <c r="V24" t="n">
-        <v>2.956699999999999</v>
+        <v>2.9529</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5846</v>
+        <v>7.554999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.628</v>
+        <v>-4.602</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104693_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104693_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.5549</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104693_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-4.602</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
